--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,57 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -722,25 +723,28 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>600</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5300</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -754,8 +758,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -763,8 +767,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,8 +811,11 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -845,8 +855,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +875,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +917,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,13 +961,16 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>17600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -958,18 +978,18 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>160200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +1005,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,12 +1022,12 @@
       <c r="F15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1017,8 +1040,8 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1026,8 +1049,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,32 +1066,33 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E17" s="3">
         <v>34600</v>
       </c>
-      <c r="E17" s="3">
-        <v>39700</v>
-      </c>
       <c r="F17" s="3">
+        <v>51300</v>
+      </c>
+      <c r="G17" s="3">
         <v>19600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>172600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,26 +1108,29 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-84500</v>
       </c>
       <c r="E18" s="3">
-        <v>-37800</v>
+        <v>-34600</v>
       </c>
       <c r="F18" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-14300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-172600</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1152,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,26 +1172,27 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>10700</v>
       </c>
       <c r="E20" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F20" s="3">
         <v>44900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>72500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-98000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1214,11 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1194,12 +1231,12 @@
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
         <v>-270600</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,26 +1258,29 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
       </c>
       <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1293,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1262,32 +1302,35 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21800</v>
       </c>
-      <c r="E23" s="3">
-        <v>7000</v>
-      </c>
       <c r="F23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G23" s="3">
         <v>58000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-271700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8600</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,13 +1346,16 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1323,11 +1369,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1344,8 +1390,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,32 +1434,35 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21800</v>
       </c>
-      <c r="E26" s="3">
-        <v>7000</v>
-      </c>
       <c r="F26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G26" s="3">
         <v>58000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-271700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8600</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,32 +1478,35 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21800</v>
       </c>
-      <c r="E27" s="3">
-        <v>7000</v>
-      </c>
       <c r="F27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G27" s="3">
         <v>58000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-271700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8600</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,8 +1522,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,31 +1566,34 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
+        <v>3500</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>11700</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1549,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,26 +1698,29 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-10700</v>
       </c>
       <c r="E32" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-44900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-72500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>98000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1672,32 +1742,35 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-271700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,8 +1786,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,32 +1830,35 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-271700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1795,37 +1874,40 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,8 +1923,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,32 +1961,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E41" s="3">
         <v>41500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,8 +2003,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1957,26 +2047,29 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,8 +2082,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -1998,8 +2091,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,13 +2135,16 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>38700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2056,15 +2155,15 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,32 +2179,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E46" s="3">
         <v>45800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>97800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>90300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,8 +2223,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2130,22 +2235,22 @@
         <v>1900</v>
       </c>
       <c r="E47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F47" s="3">
         <v>18600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>345000</v>
       </c>
       <c r="I47" s="3">
         <v>345000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>345000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2162,26 +2267,29 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E48" s="3">
         <v>9500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2194,8 +2302,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2203,26 +2311,29 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>57200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,8 +2346,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2244,8 +2355,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,8 +2443,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2367,8 +2487,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,32 +2531,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E54" s="3">
         <v>114500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>143200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>113700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>346500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>347000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2575,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,26 +2613,27 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E57" s="3">
         <v>19200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2515,8 +2646,8 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2524,31 +2655,34 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2565,13 +2699,16 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>5900</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -2582,15 +2719,15 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,32 +2743,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E60" s="3">
         <v>20800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,23 +2787,26 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2688,32 +2831,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>5900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>130500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22400</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +2875,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,32 +3007,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E66" s="3">
         <v>34300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>147600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,8 +3051,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,32 +3245,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-72200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-29900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-105100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,8 +3289,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,32 +3421,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E76" s="3">
         <v>80200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>55900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-33800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>310900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>323600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3465,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,37 +3509,40 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,32 +3558,35 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-271700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3407,8 +3602,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,8 +3622,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3465,8 +3664,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,32 +3884,35 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8100</v>
       </c>
-      <c r="E89" s="3">
-        <v>-13700</v>
-      </c>
       <c r="F89" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="G89" s="3">
         <v>-13200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,8 +3928,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,23 +3948,24 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13500</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3754,14 +3975,14 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3769,8 +3990,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,32 +4078,35 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-345000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3892,8 +4122,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4184,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,32 +4316,35 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E100" s="3">
         <v>18400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>120100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>347100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,25 +4360,28 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -4146,8 +4395,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4155,32 +4404,35 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-33200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>86800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4194,6 +4446,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,61 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,28 +727,31 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+      <c r="I8" s="3">
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -761,8 +765,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -770,8 +774,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,35 +981,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E14" s="3">
         <v>17600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>4800</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>160200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,29 +1028,32 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>1600</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+      <c r="F15" s="3">
+        <v>1200</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1043,8 +1066,8 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,35 +1093,36 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E17" s="3">
         <v>85100</v>
       </c>
-      <c r="E17" s="3">
-        <v>34600</v>
-      </c>
       <c r="F17" s="3">
+        <v>25400</v>
+      </c>
+      <c r="G17" s="3">
         <v>51300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>172600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1111,29 +1138,32 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-84500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-34600</v>
-      </c>
       <c r="F18" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-49400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-172600</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,29 +1206,30 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>10700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>44900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>72500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-98000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1217,29 +1251,32 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-14400</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+      <c r="F21" s="3">
+        <v>-11300</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>-270600</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,29 +1298,32 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1336,8 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1305,35 +1345,38 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-74000</v>
       </c>
-      <c r="E23" s="3">
-        <v>-21800</v>
-      </c>
       <c r="F23" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="G23" s="3">
         <v>-4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>58000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-271700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,17 +1392,20 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1369,14 +1415,14 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,35 +1486,38 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-73900</v>
       </c>
-      <c r="E26" s="3">
-        <v>-21800</v>
-      </c>
       <c r="F26" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>58000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-271700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,35 +1533,38 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-73900</v>
       </c>
-      <c r="E27" s="3">
-        <v>-21800</v>
-      </c>
       <c r="F27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-271700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,23 +1627,26 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E29" s="3">
         <v>3500</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F29" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G29" s="3">
         <v>11700</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1595,8 +1656,8 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,29 +1768,32 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-44900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-72500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>98000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1745,35 +1815,38 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-70400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-271700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,35 +1909,38 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-70400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-271700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,40 +1956,43 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,35 +2048,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E41" s="3">
         <v>44500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>82200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,29 +2140,32 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2085,8 +2178,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2094,8 +2187,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,17 +2234,20 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>38700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,15 +2257,15 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,35 +2281,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E46" s="3">
         <v>86300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>45800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>56600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,34 +2328,37 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E47" s="3">
         <v>1900</v>
       </c>
       <c r="F47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G47" s="3">
         <v>18600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>345000</v>
       </c>
       <c r="J47" s="3">
         <v>345000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>345000</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
@@ -2270,29 +2375,32 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2305,8 +2413,8 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2314,29 +2422,32 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E49" s="3">
         <v>3400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>57200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>30000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2460,8 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2563,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,35 +2657,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E54" s="3">
         <v>99800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>114500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>143200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>113700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>346500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>347000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,29 +2744,30 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,8 +2780,8 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2658,34 +2789,37 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>100</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2702,17 +2836,20 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2722,15 +2859,15 @@
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,35 +2883,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E60" s="3">
         <v>26800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,26 +2930,29 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E61" s="3">
         <v>6300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2834,35 +2977,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>5900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>130500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,35 +3165,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E66" s="3">
         <v>33100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>147600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,35 +3419,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-120600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-72200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-29900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-17100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-105100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-34100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,35 +3607,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E76" s="3">
         <v>66700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>78600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>55900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-33800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>310900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>323600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,40 +3701,43 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,35 +3753,38 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-70400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-271700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3821,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,35 +4101,38 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,26 +4169,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13500</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3978,14 +4199,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,35 +4308,38 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-345000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,35 +4562,38 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>44900</v>
       </c>
-      <c r="E100" s="3">
-        <v>18400</v>
-      </c>
       <c r="F100" s="3">
+        <v>19600</v>
+      </c>
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>120100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>347100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,28 +4609,31 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4398,8 +4647,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4407,35 +4656,38 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4449,6 +4701,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,68 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -730,34 +731,40 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
@@ -768,17 +775,23 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -788,11 +801,11 @@
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>600</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -800,8 +813,8 @@
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -824,8 +837,14 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,11 +854,11 @@
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-500</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -847,8 +866,8 @@
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>-700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -871,8 +890,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +915,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +964,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,19 +1017,25 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>17600</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4800</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1004,21 +1043,21 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>160200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,35 +1070,41 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+        <v>800</v>
+      </c>
+      <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
+        <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>600</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1069,17 +1114,23 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,41 +1145,43 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>85100</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F17" s="3">
-        <v>25400</v>
+        <v>10400</v>
       </c>
       <c r="G17" s="3">
-        <v>51300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>19600</v>
-      </c>
-      <c r="I17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
+        <v>16500</v>
+      </c>
+      <c r="K17" s="3">
         <v>172600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1141,35 +1194,41 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-16700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-84500</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>-25400</v>
+        <v>-10300</v>
       </c>
       <c r="G18" s="3">
-        <v>-49400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="I18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-172600</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,8 +1247,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,35 +1272,37 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>10700</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>12900</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>44900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>72500</v>
-      </c>
-      <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-98000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,35 +1321,41 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1000</v>
       </c>
       <c r="F21" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>-7500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>200</v>
       </c>
       <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-270600</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,35 +1374,41 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
       <c r="G22" s="3">
-        <v>200</v>
-      </c>
-      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,50 +1418,56 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-74000</v>
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F23" s="3">
-        <v>-12600</v>
+        <v>-8100</v>
       </c>
       <c r="G23" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-271700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-12700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1395,40 +1480,46 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1442,8 +1533,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,41 +1586,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-73900</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F26" s="3">
-        <v>-12600</v>
+        <v>-8100</v>
       </c>
       <c r="G26" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-271700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>8600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1536,41 +1639,47 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-73900</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F27" s="3">
-        <v>-12600</v>
+        <v>-23800</v>
       </c>
       <c r="G27" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I27" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-271700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-12700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>8600</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,8 +1692,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,40 +1745,46 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-31600</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-9200</v>
+        <v>-15800</v>
       </c>
       <c r="G29" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>-15800</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-4600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1677,8 +1798,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1851,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,35 +1904,41 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-10700</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>-12900</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>-44900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-72500</v>
-      </c>
-      <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K32" s="3">
         <v>98000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,41 +1957,47 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-47700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-70400</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F33" s="3">
-        <v>-21800</v>
+        <v>-23800</v>
       </c>
       <c r="G33" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I33" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-271700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>8600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,8 +2010,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,41 +2063,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-47700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-70400</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>-21800</v>
+        <v>-23800</v>
       </c>
       <c r="G35" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I35" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-271700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>8600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1959,46 +2116,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2011,8 +2174,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2199,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,41 +2220,43 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F41" s="3">
         <v>21300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>21300</v>
+      </c>
+      <c r="H41" s="3">
         <v>44500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>44500</v>
+      </c>
+      <c r="J41" s="3">
         <v>41500</v>
       </c>
-      <c r="G41" s="3">
-        <v>49000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>82200</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>87000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2269,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,35 +2322,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5600</v>
       </c>
-      <c r="E43" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>4300</v>
-      </c>
       <c r="G43" s="3">
-        <v>7700</v>
+        <v>5600</v>
       </c>
       <c r="H43" s="3">
-        <v>15600</v>
+        <v>1400</v>
       </c>
       <c r="I43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,40 +2366,46 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2237,41 +2428,47 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>38700</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="I45" s="3">
+        <v>38700</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,41 +2481,47 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F46" s="3">
         <v>29100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>29100</v>
+      </c>
+      <c r="H46" s="3">
         <v>86300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>86300</v>
+      </c>
+      <c r="J46" s="3">
         <v>45800</v>
       </c>
-      <c r="G46" s="3">
-        <v>56600</v>
-      </c>
-      <c r="H46" s="3">
-        <v>97800</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>90300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,41 +2534,47 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1900</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>18600</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>5000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>345000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>345000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2378,35 +2587,41 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H48" s="3">
         <v>8100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2416,44 +2631,50 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F49" s="3">
         <v>3700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="F49" s="3">
-        <v>57200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>40300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>30000</v>
-      </c>
       <c r="I49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>18200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2463,17 +2684,23 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2746,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,31 +2799,37 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2613,8 +2852,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,41 +2905,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>26700</v>
+      </c>
+      <c r="F54" s="3">
         <v>41800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>41800</v>
+      </c>
+      <c r="H54" s="3">
         <v>99800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>99800</v>
+      </c>
+      <c r="J54" s="3">
         <v>114500</v>
       </c>
-      <c r="G54" s="3">
-        <v>123900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>143200</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>113700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>346500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>347000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2958,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2983,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,35 +3004,37 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12400</v>
+        <v>11900</v>
       </c>
       <c r="E57" s="3">
-        <v>18800</v>
+        <v>11900</v>
       </c>
       <c r="F57" s="3">
-        <v>19200</v>
+        <v>8200</v>
       </c>
       <c r="G57" s="3">
-        <v>22700</v>
+        <v>8200</v>
       </c>
       <c r="H57" s="3">
-        <v>18900</v>
+        <v>11800</v>
       </c>
       <c r="I57" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K57" s="3">
         <v>17100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2783,50 +3044,56 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2839,41 +3106,47 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8100</v>
       </c>
       <c r="J59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,41 +3159,47 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F60" s="3">
         <v>17200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H60" s="3">
         <v>26800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>26800</v>
+      </c>
+      <c r="J60" s="3">
         <v>20800</v>
       </c>
-      <c r="G60" s="3">
-        <v>23800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>17100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,32 +3212,38 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>700</v>
+      </c>
+      <c r="F61" s="3">
         <v>5200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H61" s="3">
         <v>6300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J61" s="3">
         <v>7600</v>
       </c>
-      <c r="G61" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H61" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2980,41 +3265,47 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5900</v>
-      </c>
       <c r="G62" s="3">
-        <v>14800</v>
+        <v>4000</v>
       </c>
       <c r="H62" s="3">
-        <v>59300</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>130500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>32900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>22400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3318,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3371,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3424,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,41 +3477,47 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F66" s="3">
         <v>26500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>26500</v>
+      </c>
+      <c r="H66" s="3">
         <v>33100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>33100</v>
+      </c>
+      <c r="J66" s="3">
         <v>34300</v>
       </c>
-      <c r="G66" s="3">
-        <v>45300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>87400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>147600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>35500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>23300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3530,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3555,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3604,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3657,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3710,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,41 +3763,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-120600</v>
+        <v>-332100</v>
       </c>
       <c r="E72" s="3">
-        <v>-72200</v>
+        <v>-332100</v>
       </c>
       <c r="F72" s="3">
-        <v>-29900</v>
+        <v>-325200</v>
       </c>
       <c r="G72" s="3">
-        <v>-17100</v>
+        <v>-325200</v>
       </c>
       <c r="H72" s="3">
-        <v>-36900</v>
+        <v>-277500</v>
       </c>
       <c r="I72" s="3">
+        <v>-277500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-105100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-34100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3816,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3869,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3922,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,41 +3975,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F76" s="3">
         <v>15300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H76" s="3">
         <v>66700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>66700</v>
+      </c>
+      <c r="J76" s="3">
         <v>80200</v>
       </c>
-      <c r="G76" s="3">
-        <v>78600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>55900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-33800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>310900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>323600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,8 +4028,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,46 +4081,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3756,41 +4139,47 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-47700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-70400</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F81" s="3">
-        <v>-21800</v>
+        <v>-23800</v>
       </c>
       <c r="G81" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>58000</v>
-      </c>
-      <c r="I81" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-271700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>8600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +4192,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,31 +4217,33 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3869,8 +4266,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4319,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4372,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4425,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4478,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,41 +4531,47 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-22700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-32800</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F89" s="3">
-        <v>-8100</v>
+        <v>-11300</v>
       </c>
       <c r="G89" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="I89" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-24000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +4584,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,31 +4609,33 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1000</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-17100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4202,23 +4643,29 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4711,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,41 +4764,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-16100</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
-        <v>-17100</v>
+        <v>-200</v>
       </c>
       <c r="G94" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-345000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,8 +4817,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,31 +4842,33 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4424,8 +4891,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4944,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4997,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,41 +5050,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>44900</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
-        <v>19600</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>21000</v>
-      </c>
-      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K100" s="3">
         <v>120100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>347100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4612,34 +5103,40 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-500</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="H101" s="3">
-        <v>900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
+        <v>500</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4650,50 +5147,56 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-23100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-7500</v>
+        <v>-11600</v>
       </c>
       <c r="G102" s="3">
-        <v>-33200</v>
+        <v>-11600</v>
       </c>
       <c r="H102" s="3">
-        <v>-4800</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K102" s="3">
         <v>86800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,6 +5207,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -1082,10 +1082,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1333,10 +1333,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>-7500</v>
@@ -2334,10 +2334,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="E43" s="3">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F43" s="3">
         <v>5600</v>
@@ -2652,10 +2652,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="E49" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="F49" s="3">
         <v>3700</v>
@@ -3012,10 +3012,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11900</v>
+        <v>9000</v>
       </c>
       <c r="E57" s="3">
-        <v>11900</v>
+        <v>9000</v>
       </c>
       <c r="F57" s="3">
         <v>8200</v>
@@ -3117,11 +3117,11 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
       </c>
       <c r="F59" s="3">
         <v>2300</v>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,75 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,40 +738,46 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
@@ -781,47 +788,53 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,38 +856,44 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="D10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>-500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-500</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>-700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -896,8 +915,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +942,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,8 +997,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,8 +1056,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1049,21 +1088,21 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>160200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,41 +1115,47 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,17 +1165,23 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,47 +1198,49 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="D17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <v>10400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>16500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>172600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,41 +1253,47 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="D18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-10300</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-172600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1312,14 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,41 +1339,43 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-10300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-98000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,41 +1394,47 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-270600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,41 +1453,47 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1424,56 +1503,62 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="D23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-8100</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>-6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-271700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-12700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>8600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,8 +1571,14 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1512,20 +1603,20 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1539,8 +1630,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,47 +1689,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="D26" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
         <v>-8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8100</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>-6300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-271700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-12700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>8600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,47 +1748,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="D27" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-23800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-23800</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-271700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-12700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>8600</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1807,14 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1866,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1763,34 +1884,34 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-15800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-15800</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-4600</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1804,8 +1925,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1984,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,41 +2043,47 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>10300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>98000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1963,47 +2102,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="D33" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-23800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-23800</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>-10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-271700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>8600</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2161,14 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,47 +2220,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="D35" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-23800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-23800</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>-10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-271700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>8600</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,52 +2279,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2343,14 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2370,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,47 +2393,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F41" s="3">
         <v>18700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>21300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>21300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>44500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>44500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>41500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>87000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2448,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2328,41 +2507,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>4500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2372,17 +2557,23 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2407,11 +2598,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2434,8 +2625,14 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2451,30 +2648,30 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>38700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>38700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,47 +2684,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F46" s="3">
         <v>23700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>23700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>29100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>29100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>86300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>86300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>45800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>90300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2540,8 +2743,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2551,11 +2760,11 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -2567,20 +2776,20 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>5000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>345000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>345000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,41 +2802,47 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,50 +2852,56 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>18200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,17 +2911,23 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2979,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,8 +3038,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2816,26 +3055,26 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>1900</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2858,8 +3097,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,47 +3156,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F54" s="3">
         <v>26700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>26700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>41800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>41800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>99800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>99800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>114500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>113700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>346500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>347000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3215,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3242,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,41 +3265,43 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F57" s="3">
         <v>9000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>11800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>17100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3050,17 +3311,23 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3071,35 +3338,35 @@
         <v>300</v>
       </c>
       <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>300</v>
+      </c>
+      <c r="H58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3112,47 +3379,53 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,47 +3438,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F60" s="3">
         <v>12200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>17200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>26800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>26800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,38 +3497,44 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>600</v>
+      </c>
+      <c r="F61" s="3">
         <v>700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3271,8 +3556,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3283,35 +3574,35 @@
         <v>2000</v>
       </c>
       <c r="F62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H62" s="3">
         <v>4000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4000</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>130500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>32900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>22400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3615,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3674,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3733,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,47 +3792,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F66" s="3">
         <v>14900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>26500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>26500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>33100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>33100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>34300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>147600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>35500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>23300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3851,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3878,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3933,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3992,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +4051,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,47 +4110,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-349300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-349300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-332100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-332100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-325200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-325200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-277500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-277500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-229000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-105100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-34100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +4169,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4228,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4287,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,47 +4346,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>66700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>66700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>80200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-33800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>310900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>323600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4405,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,52 +4464,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,47 +4528,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="D81" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-23800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-23800</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>-10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-271700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>8600</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4587,14 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,37 +4614,39 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4272,8 +4669,14 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4728,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4787,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4846,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4905,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,47 +4964,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-11300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-11300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-24000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +5023,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,61 +5050,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +5164,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,47 +5223,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>200</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-345000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +5282,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5309,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4870,11 +5337,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4897,8 +5364,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5423,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5482,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,47 +5541,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="D100" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>9800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>120100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>347100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,40 +5600,46 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -5153,56 +5650,62 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-11600</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>86800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5213,6 +5716,12 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,82 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,46 +746,52 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
@@ -794,53 +802,59 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,44 +876,50 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>-500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-500</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>-700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +941,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,8 +970,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1003,8 +1031,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1096,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,21 +1134,21 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>160200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,47 +1161,53 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,17 +1217,23 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,53 +1252,55 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>16500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>172600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,47 +1313,53 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6600</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-10300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10300</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-16500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-172600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1378,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,47 +1407,49 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-10300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-98000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,47 +1468,53 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-270600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,47 +1533,53 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,62 +1589,68 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8600</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-8100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-271700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>8600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1663,14 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1609,20 +1701,20 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1636,8 +1728,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,53 +1793,59 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-8600</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-8100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-8100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-271700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-12700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>8600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,53 +1858,59 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-8600</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-23800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-23800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-271700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>8600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1923,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1988,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1890,34 +2012,34 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-15800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-15800</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-4600</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -1931,8 +2053,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2118,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,47 +2183,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>10300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>98000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,53 +2248,59 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-8600</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-23800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-23800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-271700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>8600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2313,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,53 +2378,59 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-8600</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-23800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-23800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-271700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>8600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,58 +2443,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2513,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2542,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,53 +2567,55 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F41" s="3">
         <v>24800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>24800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>44500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>44500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>41500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>87000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2628,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2513,47 +2693,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2563,17 +2749,23 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2604,11 +2796,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2631,8 +2823,14 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2654,30 +2852,30 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>38700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>38700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,53 +2888,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F46" s="3">
         <v>26600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>26600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>23700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>29100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>86300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>86300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>45800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>90300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2953,14 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2766,11 +2976,11 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
@@ -2782,20 +2992,20 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>5000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>345000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>345000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,47 +3018,53 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,56 +3074,62 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F49" s="3">
         <v>1900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3400</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>18200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,17 +3139,23 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3213,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,8 +3278,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3061,26 +3301,26 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1900</v>
       </c>
       <c r="L52" s="3">
         <v>1900</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3103,8 +3343,14 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,53 +3408,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F54" s="3">
         <v>29400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>26700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>26700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>41800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>41800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>99800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>99800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>114500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>113700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>346500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>347000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3473,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3502,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,47 +3527,49 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>13300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>17100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3317,17 +3579,23 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3344,35 +3612,35 @@
         <v>300</v>
       </c>
       <c r="H58" s="3">
+        <v>300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
         <v>2400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,53 +3653,59 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>8100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>2500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,53 +3718,59 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F60" s="3">
         <v>10800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>12200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>12200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>26800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,44 +3783,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>500</v>
+      </c>
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3562,16 +3848,22 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
         <v>2000</v>
@@ -3580,35 +3872,35 @@
         <v>2000</v>
       </c>
       <c r="H62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>130500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>32900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>22400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3913,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3978,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +4043,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,53 +4108,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F66" s="3">
         <v>13400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>13400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>26500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>26500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>33100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>33100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>34300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>147600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>35500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>23300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4173,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4202,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4263,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4328,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4393,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,53 +4458,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-373800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-373800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-349300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-349300</v>
       </c>
-      <c r="F72" s="3">
-        <v>-332100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-332100</v>
-      </c>
       <c r="H72" s="3">
+        <v>-338500</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-338500</v>
+      </c>
+      <c r="J72" s="3">
         <v>-325200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-325200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-277500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-277500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-229000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-105100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-34100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4523,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4588,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4653,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,53 +4718,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F76" s="3">
         <v>16000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>16000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>15300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>66700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>66700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>80200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-33800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>310900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>323600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4783,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,58 +4848,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,53 +4918,59 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-8600</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-23800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-23800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-271700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>8600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4983,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,44 +5012,46 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -4675,8 +5073,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +5138,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +5203,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5268,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5333,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5398,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-11300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-11300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-24000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5463,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,67 +5492,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5618,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5683,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-345000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5748,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5777,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5343,11 +5811,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5370,8 +5838,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5903,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5968,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +6033,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>9100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>9800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>120100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>347100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,46 +6098,52 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5656,62 +6154,68 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-11600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-11600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>86800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +6226,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARQQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="92">
   <si>
     <t>ARQQ</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,52 +753,58 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
@@ -808,59 +815,65 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,50 +895,56 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>-500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>-700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +966,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +997,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,8 +1064,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1135,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1140,21 +1179,21 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>160200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1167,53 +1206,59 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,17 +1268,23 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,59 +1305,61 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>10400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3">
         <v>16500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>172600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,53 +1372,59 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-10300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-16500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-172600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1443,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,53 +1474,55 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-10300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-98000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,53 +1541,59 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-270600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,53 +1612,59 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1595,68 +1674,74 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-271700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>8600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,16 +1754,22 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1707,20 +1798,20 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1734,8 +1825,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,59 +1896,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>-8100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3">
         <v>-6300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-271700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>8600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,59 +1967,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>-23800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-23800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-271700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>8600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +2038,14 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2109,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2018,34 +2139,34 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-15800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-15800</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-4600</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2059,8 +2180,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2251,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,53 +2322,59 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>10300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>98000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,59 +2393,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>-23800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-23800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3">
         <v>-10900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-271700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>8600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2464,14 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,59 +2535,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>-23800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-23800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3">
         <v>-10900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-271700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>8600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,64 +2606,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2682,14 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2713,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,59 +2740,61 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F41" s="3">
         <v>37000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>37000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>24800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>24800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>18700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>21300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>44500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>44500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>41500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>87000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2807,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,53 +2878,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,17 +2940,23 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2802,11 +2993,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2829,8 +3020,14 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2858,30 +3055,30 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>38700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>38700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,59 +3091,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F46" s="3">
         <v>40000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>40000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>26600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>26600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>86300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>86300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>45800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>90300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3162,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2982,11 +3191,11 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2998,20 +3207,20 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>345000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>345000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,53 +3233,59 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>9500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,62 +3295,68 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3400</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>18200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,17 +3366,23 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3446,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,8 +3517,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3307,26 +3546,26 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1900</v>
       </c>
       <c r="N52" s="3">
         <v>1900</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3349,8 +3588,14 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,59 +3659,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F54" s="3">
         <v>42900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>42900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>26700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>26700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>41800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>41800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>99800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>99800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>114500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>113700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>346500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>347000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3730,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3761,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,53 +3788,55 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>11800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,25 +3846,31 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
@@ -3618,35 +3885,35 @@
         <v>300</v>
       </c>
       <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,59 +3926,65 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3">
         <v>11400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>2500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,59 +3997,65 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F60" s="3">
         <v>14900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>26800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>26800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>17100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,50 +4068,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3854,22 +4139,28 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2000</v>
       </c>
       <c r="H62" s="3">
         <v>2000</v>
@@ -3878,35 +4169,35 @@
         <v>2000</v>
       </c>
       <c r="J62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>130500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>32900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>22400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4210,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4281,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4352,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,59 +4423,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F66" s="3">
         <v>15600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>13400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>26500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>26500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>33100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>33100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>34300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>147600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>35500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>23300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4494,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4525,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4592,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4663,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4734,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,59 +4805,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-406900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-406900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-373800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-373800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-349300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-349300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-338500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-338500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-325200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-325200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-277500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-277500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-229000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-105100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>5000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4876,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4947,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +5018,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,59 +5089,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>28500</v>
+      </c>
+      <c r="F76" s="3">
         <v>27200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>27200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>16000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>66700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>66700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>80200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-33800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>310900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>323600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +5160,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,64 +5231,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,59 +5307,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>-23800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-23800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3">
         <v>-10900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-271700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>8600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5378,14 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,50 +5409,52 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5079,8 +5476,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5547,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5618,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5689,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5760,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,59 +5831,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-11300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-11300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-24000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5902,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,73 +5933,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +6071,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,59 +6142,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
         <v>200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="E94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
+        <v>200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>200</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-8600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-345000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +6213,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6244,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5817,11 +6284,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5844,8 +6311,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6382,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6453,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,59 +6524,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>9100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>9100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>9800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>120100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>347100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,52 +6595,58 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -6160,68 +6657,74 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-11600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>86800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6735,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
